--- a/reporte.xlsx
+++ b/reporte.xlsx
@@ -316,9 +316,9 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>47625</colOff>
+      <colOff>0</colOff>
       <row>0</row>
-      <rowOff>114300</rowOff>
+      <rowOff>120000</rowOff>
     </from>
     <ext cx="1905000" cy="476250"/>
     <pic>
@@ -687,13 +687,13 @@
     <col width="120" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
-    <row r="1" ht="64" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Empresa: Bimsa Reports
 Usuario: Alejandro Ortega
-Fecha de descarga: 05-03-2026
+Fecha de descarga: 06-03-2026
 Descarga por Fecha de publicación del 2026-01-01 al 2026-01-31</t>
         </is>
       </c>

--- a/reporte.xlsx
+++ b/reporte.xlsx
@@ -318,7 +318,7 @@
       <col>0</col>
       <colOff>0</colOff>
       <row>0</row>
-      <rowOff>120000</rowOff>
+      <rowOff>140000</rowOff>
     </from>
     <ext cx="1905000" cy="476250"/>
     <pic>
@@ -687,7 +687,7 @@
     <col width="120" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="70" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="2" t="inlineStr">
         <is>

--- a/reporte.xlsx
+++ b/reporte.xlsx
@@ -318,7 +318,7 @@
       <col>0</col>
       <colOff>0</colOff>
       <row>0</row>
-      <rowOff>140000</rowOff>
+      <rowOff>180000</rowOff>
     </from>
     <ext cx="1905000" cy="476250"/>
     <pic>
@@ -687,7 +687,7 @@
     <col width="120" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
-    <row r="1" ht="70" customHeight="1">
+    <row r="1" ht="80" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="2" t="inlineStr">
         <is>

--- a/reporte.xlsx
+++ b/reporte.xlsx
@@ -693,7 +693,7 @@
         <is>
           <t>Empresa: Bimsa Reports
 Usuario: Alejandro Ortega
-Fecha de descarga: 06-03-2026
+Fecha de descarga: 09-03-2026
 Descarga por Fecha de publicación del 2026-01-01 al 2026-01-31</t>
         </is>
       </c>
